--- a/inv/men_innerwear.xlsx
+++ b/inv/men_innerwear.xlsx
@@ -14,66 +14,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Title</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>titleid</t>
   </si>
   <si>
-    <t>men_accessories</t>
-  </si>
-  <si>
-    <t>Men Accessories</t>
-  </si>
-  <si>
-    <t>men_shoes</t>
-  </si>
-  <si>
-    <t>Men Shoes</t>
-  </si>
-  <si>
-    <t>men_bags</t>
-  </si>
-  <si>
-    <t>Men Bags</t>
-  </si>
-  <si>
-    <t>men_eyewear</t>
-  </si>
-  <si>
-    <t>Men Eyewear</t>
-  </si>
-  <si>
-    <t>men_footwear</t>
-  </si>
-  <si>
-    <t>Men FooteWear</t>
-  </si>
-  <si>
-    <t>men_jewellery</t>
-  </si>
-  <si>
-    <t>Men Jewellery</t>
-  </si>
-  <si>
-    <t>men_belts</t>
-  </si>
-  <si>
-    <t>Men Belts</t>
-  </si>
-  <si>
-    <t>men_wallets</t>
-  </si>
-  <si>
-    <t>Men Wallets</t>
-  </si>
-  <si>
-    <t>men_innerwear</t>
-  </si>
-  <si>
-    <t>Men Innerwear</t>
+    <t>title</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>scat</t>
+  </si>
+  <si>
+    <t>image</t>
   </si>
 </sst>
 </file>
@@ -405,90 +360,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="E1" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
